--- a/data/data_dict-hrh_aggregated.xlsx
+++ b/data/data_dict-hrh_aggregated.xlsx
@@ -1107,7 +1107,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>&lt;StringArray&gt;
+          <t>&lt;ArrowStringArray&gt;
 ['nurse-anes', 'pt-assist', 'mt', 'pt', 'ph-practictioner']
 Length: 5, dtype: str</t>
         </is>
